--- a/data/demo/Tecnolink-Traffic-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/Tecnolink-Traffic-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="181">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,16 +23,16 @@
     <t>TIANLAI Ventilador de techo ahorrador de energía de 10 pulgadas con luz LED de 1900 lm, 2 en 1 Lampara Ventilador Silenciosa, Instalación Sin Taladrar, Ideal para Dormitorio y Espacios Pequeños, socket E27, fácil instalación, ideal para dormitorio, cocina, despensa.</t>
   </si>
   <si>
-    <t>166380</t>
-  </si>
-  <si>
-    <t>138503</t>
-  </si>
-  <si>
-    <t>2593</t>
-  </si>
-  <si>
-    <t>2369</t>
+    <t>248180</t>
+  </si>
+  <si>
+    <t>204146</t>
+  </si>
+  <si>
+    <t>3861</t>
+  </si>
+  <si>
+    <t>3508</t>
   </si>
   <si>
     <t>1.56%</t>
@@ -44,40 +44,61 @@
     <t>TIANLAI Lámpara LED blanca de 6500K, con luz suave, con conector en rosca E27 estándar, es fácil de instalar, tiene una potencia de 10 vatios, es energéticamente eficiente y tiene una hermética sellación, tiene una larga duración útil. Es adecuada para la iluminación interior y se puede utilizar en hogares y oficinas.</t>
   </si>
   <si>
-    <t>119704</t>
-  </si>
-  <si>
-    <t>97310</t>
-  </si>
-  <si>
-    <t>1395</t>
-  </si>
-  <si>
-    <t>1273</t>
-  </si>
-  <si>
-    <t>1.17%</t>
+    <t>181458</t>
+  </si>
+  <si>
+    <t>145228</t>
+  </si>
+  <si>
+    <t>2065</t>
+  </si>
+  <si>
+    <t>1882</t>
+  </si>
+  <si>
+    <t>1.14%</t>
   </si>
   <si>
     <t>604682772656414</t>
   </si>
   <si>
-    <t>Wireless Bluetooth 5.3 TWS Earbuds with Clear HD LED Digital Battery Screen, Compatible with iOS Android, Ideal for Gaming Calling Music, 5 Hours Single Playtime, Charging Case Supports 6 Recharges, 4 CVC8.0 Noise Reduction Microphones, Hi-Fi Stereo Sound</t>
-  </si>
-  <si>
-    <t>29019</t>
-  </si>
-  <si>
-    <t>23852</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>1.37%</t>
+    <t>Clear HD LED Digital Battery Screen Wireless Bluetooth 5.3 TWS Earbuds, Compatible with iOS Android, Ideal for Gaming Calling Music, 5 Hours Single Playtime, Charging Case Supports 6 Recharges, 4 CVC8.0 Noise Reduction Microphones, Hi-Fi Stereo Sound</t>
+  </si>
+  <si>
+    <t>29654</t>
+  </si>
+  <si>
+    <t>24248</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>1.39%</t>
+  </si>
+  <si>
+    <t>604564661057091</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Lámpara de Techo E27 18 cm/26 cm, Versiones 18W/24W Ahorradora de Energía, 3 Temperaturas de Color, Diseño de Cielo Estrellado con Diamantes, Fácil Instalación, Ideal para 6-15㎡ Dormitorios/Comedores/Pasillos, Vida Útil 50000h</t>
+  </si>
+  <si>
+    <t>6576</t>
+  </si>
+  <si>
+    <t>4993</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>2.86%</t>
   </si>
   <si>
     <t>604584525290571</t>
@@ -86,19 +107,19 @@
     <t>TIANLAI Foco LED 12W/15W Paquete de 10, Ahorro Energético Reemplazo 60W/65W, 6500K Luz Fría 880LM/1200LM, Sin Parpadeo Base E26/E27 Universal, 50000H Vida Útil para Hogar Oficina</t>
   </si>
   <si>
-    <t>3329</t>
-  </si>
-  <si>
-    <t>2556</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>2.40%</t>
+    <t>4805</t>
+  </si>
+  <si>
+    <t>3691</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>2.46%</t>
   </si>
   <si>
     <t>608388742240448</t>
@@ -107,19 +128,40 @@
     <t>Altavoz Bluetooth Portátil Linkbits, Parlante Inalámbrico Estéreo Diseño Aluminio, Sonido Nítido, Radio FM, Interfaces USB AUX, Bocina Portátil para Relajación en Casa y Fiestas Exteriores</t>
   </si>
   <si>
-    <t>6002</t>
-  </si>
-  <si>
-    <t>4864</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>1.47%</t>
+    <t>9839</t>
+  </si>
+  <si>
+    <t>7828</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>1.54%</t>
+  </si>
+  <si>
+    <t>605296634249545</t>
+  </si>
+  <si>
+    <t>TIANLAI Reflector LED 20W (1800LM) y 30W (2700LM) Vida Útil 50,000 Horas Ángulo 120° Eficiente Energía Instalación Fácil para Interior y Exterior</t>
+  </si>
+  <si>
+    <t>7285</t>
+  </si>
+  <si>
+    <t>5716</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>2.77%</t>
   </si>
   <si>
     <t>605403471556246</t>
@@ -128,40 +170,40 @@
     <t>【TIANLAI】Lámpara de Techo E27 de 7.1" – Ahorro de Energía 18W, 3 Temperaturas de Color, Diseño de Cielo Estrellado Diamante, Fácil Instalación, Ideal para Dormitorios, Comedores y Pasillos de 6-10㎡, Duración de 50000h</t>
   </si>
   <si>
-    <t>4724</t>
-  </si>
-  <si>
-    <t>3491</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>2.58%</t>
-  </si>
-  <si>
-    <t>605296634249545</t>
-  </si>
-  <si>
-    <t>TIANLAI Reflector LED 20W (1800LM) y 30W (2700LM) Vida Útil 50,000 Horas Ángulo 220° Eficiente Energía Instalación Fácil para Interior y Exterior</t>
-  </si>
-  <si>
-    <t>4918</t>
-  </si>
-  <si>
-    <t>3912</t>
+    <t>6994</t>
+  </si>
+  <si>
+    <t>5077</t>
+  </si>
+  <si>
+    <t>182</t>
   </si>
   <si>
     <t>149</t>
   </si>
   <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>3.03%</t>
+    <t>2.60%</t>
+  </si>
+  <si>
+    <t>604549897144935</t>
+  </si>
+  <si>
+    <t>TIANLAI Ventilador portátil recargable con luz LED, ventilador de camping portátil con luz, incluye control remoto y gancho de suspensión. Cuenta con 3 velocidades de viento y 3 modos de iluminación. Fácil de instalar, desmontar y limpiar. Ideal para camping, actividades al aire libre, viajes, pesca, dormitorio, sala, cocina y almacén.</t>
+  </si>
+  <si>
+    <t>1699</t>
+  </si>
+  <si>
+    <t>1422</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>2.88%</t>
   </si>
   <si>
     <t>605485126274947</t>
@@ -170,388 +212,349 @@
     <t>TIANLAI Luz UV 20W/25W, Lampara UVC Esterilizadora, Bombilla Germicida 360°, Purificador de Ambientes para Hogar, Recamara, Baño, Cocina, Alimentacion por Enchufe y Base E27</t>
   </si>
   <si>
-    <t>1099</t>
-  </si>
-  <si>
-    <t>927</t>
+    <t>1613</t>
+  </si>
+  <si>
+    <t>1347</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>3.66%</t>
+  </si>
+  <si>
+    <t>604566808544081</t>
+  </si>
+  <si>
+    <t>TIANLAI Tiras LED de 5M para Interior - Alta luminosidad de 4500lm-8000lm, CRI&gt;70, Seguro de baja tensión 12V, Flexibles y fáciles de cortar/instalar para decoración hogareña</t>
+  </si>
+  <si>
+    <t>26813</t>
+  </si>
+  <si>
+    <t>23402</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>1.50%</t>
+  </si>
+  <si>
+    <t>605217764561200</t>
+  </si>
+  <si>
+    <t>Tianlai Lámpara LED con Ventilador, 2 en 1 ventilador y lámpara LED，Ventilador portátil y luz LED，Diseño Integrado,Fácil de instalar, desmontar y limpiar. Ideal para camping, actividades al aire libre, viajes, pesca, dormitorio, sala, cocina y almacén， Lámpara de Ventilador Colgante, Estilo Fácil, Fácil Instalación, Adecuada para Baño, Dormitorio, Estudio, Sala de Estar, Comedor</t>
+  </si>
+  <si>
+    <t>9645</t>
+  </si>
+  <si>
+    <t>8426</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>3.60%</t>
+  </si>
+  <si>
+    <t>605332923343861</t>
+  </si>
+  <si>
+    <t>TIANLAI 41 cm Ventilador de techo retráctil con luz - Control remoto, ultra silencioso, 3 temperaturas de color regulables, base E27 para recámara, sala y comedor</t>
+  </si>
+  <si>
+    <t>5091</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>604713374298760</t>
+  </si>
+  <si>
+    <t>TIANLAI Lámpara de Trabajo LED Recargable, 360° Giratoria con Imán Ultrapotente, 2 Modos de Luz COB + 1 Modo Frontal, Multipropósito para Mecánica Camping Reparaciones, Regalo Perfecto para San Valentín Día del Padre</t>
+  </si>
+  <si>
+    <t>3470</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1.59%</t>
+  </si>
+  <si>
+    <t>605123275288511</t>
+  </si>
+  <si>
+    <t>Altavoz de Karaoke Portátil Bluetooth, Máquina de karaoke con micrófono inalámbrico, Efectos de Luz RGB, karaoke portátil para reuniones, fiestas, regalo de Navidad, máquina de karaoke portátil para adultos/micrófono de karaoke con luces LED, altavoz de karaoke compatible con tarjeta TF/USB</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1.74%</t>
+  </si>
+  <si>
+    <t>604676867070503</t>
+  </si>
+  <si>
+    <t>TIANLAI Foco LED 3 Aspas Plegable 28W, Lámpara LED de 3 Alas Plegables con Base E27, Luz Blanca Fría 6500K, Ahorrador de Energía para Garaje, Taller y Hogar</t>
+  </si>
+  <si>
+    <t>5142</t>
+  </si>
+  <si>
+    <t>4364</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2.06%</t>
+  </si>
+  <si>
+    <t>605310374743727</t>
+  </si>
+  <si>
+    <t>TIANLAI Foco Recargable LED, Lámpara de Emergencia Portátil 75W(120lm)/120W(200lm)/180W(260lm) con 3 Modos de Luz (Alta/Baja/SOS), Colgante para Campamento, Cortes de Luz, Pesca y Puestos</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>3.24%</t>
+  </si>
+  <si>
+    <t>604405965361382</t>
+  </si>
+  <si>
+    <t>AMABLELUZ Reflector LED RGB，30W, 2200LM, Ángulo De Haz 120°, Vida Útil 50,000Horas, Foco De Inundación Con Cambio De Color Y Control Remoto, Fácil Instalación Para Uso Interior Y Exterior</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>604713374312366</t>
+  </si>
+  <si>
+    <t>Mascarillas Infantiles KF94 10 pcs, Cuatro Capas de Protección con Tejido de Fusión Filtrante, Patrones Divertidos, Piel Amigable y Transpirable</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>2.11%</t>
+  </si>
+  <si>
+    <t>604758890925204</t>
+  </si>
+  <si>
+    <t>MEGALUZ Lámpara Techo Empotrada LED 18W , Luz Fría 6500K Ajustable, Cuerpo Ultradelgado, Tamaño de Abertura Ajustable, Hecha de Aleación de Aluminio de Alta Calidad, Anticorrosivo y Antirroto, Voltaje de Trabajo 85-265V/60Hz, Ideal para Sala, Dormitorio, Escalera y Pasillo</t>
+  </si>
+  <si>
+    <t>657</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>2.28%</t>
+  </si>
+  <si>
+    <t>604862842503270</t>
+  </si>
+  <si>
+    <t>Megaluz Ventilador de techo con luz led y control remoto, 13”, luz blanca fría, neutra y cálida, 6 aspas desmontables, Abanico de techo enchufe E27, 4 velocidades y motor silencioso (Blanco)</t>
+  </si>
+  <si>
+    <t>3159</t>
+  </si>
+  <si>
+    <t>2450</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>3.20%</t>
+  </si>
+  <si>
+    <t>604986910049088</t>
+  </si>
+  <si>
+    <t>TIANLAI Ventilador de Techo con Luz E27 10", 2 en 1 Lampara Ventilador Silenciosa, Instalación Sin Taladrar, Ideal para Dormitorio y Espacios Pequeños，Silent 2-In-1 Ceiling Fan Lamp, Modern Design, Freshness, And Brightness for All Year Round, Ideal Solution for Small And Hot Spaces, Enjoy a Cool Summer, Ideal for Interiors, Living Room, Garage, Closet, Laundry Room, Bedroom, And Bathroom.</t>
+  </si>
+  <si>
+    <t>605025514435220</t>
+  </si>
+  <si>
+    <t>Linkbits Auriculares inalámbricos de orejas de gato con Inalámbrico 5.3, luces RGB, conductores de 40 mm para sonido Hi-Fi, batería de larga duración de 10 horas, botones multifuncionales, ideales para juegos y música, compatibles con tarjeta TF y entrada AUX, y con diseño plegable y portátil</t>
+  </si>
+  <si>
+    <t>605056434809577</t>
+  </si>
+  <si>
+    <t>linkbit Audífonos Inalámbricos de Diadema Bluetooth 6.0 - Baja Latencia para Música y Juegos, Audio Hi-Res con Driver de 40mm, Plegable para Hogar, Oficina y Viajes</t>
+  </si>
+  <si>
+    <t>605174814855085</t>
+  </si>
+  <si>
+    <t>Cámara de Seguridad WiFi HD: Cámara de vigilancia con visión panorámica de 355°, visión nocturna a color HD y control remoto, para interior y exterior. Cuenta con sistema de seguridad para el hogar, control mediante aplicación móvil, alertas de alarma en tiempo real y monitoreo remoto. Ideal para viviendas, oficinas y granjas.</t>
+  </si>
+  <si>
+    <t>784</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>2.04%</t>
+  </si>
+  <si>
+    <t>605180133239039</t>
+  </si>
+  <si>
+    <t>Linkbits Brazo de Monitor de Movimiento Completo, Soporta 1 o 2 Monitores/TV, Soporte de Resorte de Gas Ajustable con Inclinación/Giro/Rotación, Carga Máxima 12kg/26.4 lbs, Apto para Pantallas Planas/Curvas de 17-32", 2 Opciones de Montaje, Gestión de Cables, Robusto y Estable</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>30.00%</t>
+  </si>
+  <si>
+    <t>605180133257498</t>
+  </si>
+  <si>
+    <t>Linkbits Auriculares Inalámbricos De Tapa Completa Con Wireless 5.0, Transductores De 40mm Para Audio De Alta Resolución, Reducción De Ruido En Llamadas ENC, Almohadillas De Piel De Proteína Ultra Suaves, Ajuste Multidimensional Y Dobles Modos (Música/Juego)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>605252929601306</t>
+  </si>
+  <si>
+    <t>Cozyna Calefactor Eléctrico con Ventilador 2 en 1, 750W/1500W, Protección Sobrecalentamiento, Compacto y Energéticamente Eficiente para Hogar y Oficina</t>
+  </si>
+  <si>
+    <t>66.67%</t>
+  </si>
+  <si>
+    <t>605406743132022</t>
+  </si>
+  <si>
+    <t>TIANLAI Luz Solar de Calle con Carga Automática, Resistente al Agua IP65, Detección de Movimiento Inteligente, Iluminación para Casa, Comunidad y Camino Rural, Sin Costos de Electricidad</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>2.05%</t>
+  </si>
+  <si>
+    <t>605447276868345</t>
+  </si>
+  <si>
+    <t>Linkbits Altavoz Portátil- Luces Ambientales Coloridas 360°, Conexión TWS, Driver de Rango Completo 57mm, Graves Potentes, Batería 1500mAh con 10 Horas de Reproducción y Reproducción Sin Conexión</t>
+  </si>
+  <si>
+    <t>1824</t>
+  </si>
+  <si>
+    <t>1501</t>
   </si>
   <si>
     <t>47</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>4.28%</t>
-  </si>
-  <si>
-    <t>605332923343861</t>
-  </si>
-  <si>
-    <t>TIANLAI 41 cm Ventilador de techo retráctil con luz - Control remoto, ultra silencioso, 3 temperaturas de color regulables, base E27 para recámara, sala y comedor</t>
-  </si>
-  <si>
-    <t>3457</t>
-  </si>
-  <si>
-    <t>2814</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>2.43%</t>
-  </si>
-  <si>
-    <t>604713374298760</t>
-  </si>
-  <si>
-    <t>TIANLAI Lámpara de Trabajo LED Recargable, 360° Giratoria con Imán Ultrapotente, 2 Modos de Luz COB + 1 Modo Frontal, Multipropósito para Mecánica Camping Reparaciones, Regalo Perfecto para San Valentín Día del Padre</t>
-  </si>
-  <si>
-    <t>2074</t>
-  </si>
-  <si>
-    <t>1787</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>1.74%</t>
-  </si>
-  <si>
-    <t>605123275288511</t>
-  </si>
-  <si>
-    <t>Altavoz de Karaoke Portátil Bluetooth, Máquina de karaoke con micrófono inalámbrico, Efectos de Luz RGB, karaoke portátil para reuniones, fiestas, regalo de Navidad, máquina de karaoke portátil para adultos/micrófono de karaoke con luces LED, altavoz de karaoke compatible con tarjeta TF/USB</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1.73%</t>
-  </si>
-  <si>
-    <t>605310374743727</t>
-  </si>
-  <si>
-    <t>TIANLAI Foco Recargable LED, Lámpara de Emergencia Portátil 75W(120lm)/120W(200lm)/180W(260lm) con 3 Modos de Luz (Alta/Baja/SOS), Colgante para Campamento, Cortes de Luz, Pesca y Puestos</t>
-  </si>
-  <si>
-    <t>428</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>3.50%</t>
-  </si>
-  <si>
-    <t>605217764561200</t>
-  </si>
-  <si>
-    <t>Tianlai Lámpara LED con Ventilador, 2 en 1 ventilador y lámpara LED，Ventilador portátil y luz LED，Diseño Integrado,Fácil de instalar, desmontar y limpiar. Ideal para camping, actividades al aire libre, viajes, pesca, dormitorio, sala, cocina y almacén， Lámpara de Ventilador Colgante, Estilo Fácil, Fácil Instalación, Adecuada para Baño, Dormitorio, Estudio, Sala de Estar, Comedor</t>
-  </si>
-  <si>
-    <t>6442</t>
-  </si>
-  <si>
-    <t>5673</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>3.48%</t>
-  </si>
-  <si>
-    <t>604676867070503</t>
-  </si>
-  <si>
-    <t>TIANLAI Foco LED 3 Aspas Plegable 28W, Lámpara LED de 3 Alas Plegables con Base E27, Luz Blanca Fría 6500K, Ahorrador de Energía para Garaje, Taller y Hogar</t>
-  </si>
-  <si>
-    <t>3337</t>
-  </si>
-  <si>
-    <t>2853</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>2.04%</t>
-  </si>
-  <si>
-    <t>604566808544081</t>
-  </si>
-  <si>
-    <t>TIANLAI Tiras LED de 5M para Interior - Alta luminosidad de 4500lm-8000lm, CRI&gt;70, Seguro de baja tensión 12V, Flexibles y fáciles de cortar/instalar para decoración hogareña</t>
-  </si>
-  <si>
-    <t>16174</t>
-  </si>
-  <si>
-    <t>14213</t>
-  </si>
-  <si>
-    <t>264</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>1.63%</t>
-  </si>
-  <si>
-    <t>604405965361382</t>
-  </si>
-  <si>
-    <t>AMABLELUZ Reflector LED RGB，30W, 2200LM, Ángulo De Haz 120°, Vida Útil 50,000Horas, Foco De Inundación Con Cambio De Color Y Control Remoto, Fácil Instalación Para Uso Interior Y Exterior</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>604549897144935</t>
-  </si>
-  <si>
-    <t>TIANLAI Ventilador portátil recargable con luz LED, ventilador de camping portátil con luz, incluye control remoto y gancho de suspensión. Cuenta con 3 velocidades de viento y 3 modos de iluminación. Fácil de instalar, desmontar y limpiar. Ideal para camping, actividades al aire libre, viajes, pesca, dormitorio, sala, cocina y almacén.</t>
-  </si>
-  <si>
-    <t>1172</t>
-  </si>
-  <si>
-    <t>967</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>3.41%</t>
-  </si>
-  <si>
-    <t>604564661057091</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Lámpara de Techo E27 18 cm/26 cm, Versiones 18W/24W Ahorradora de Energía, 3 Temperaturas de Color, Diseño de Cielo Estrellado con Diamantes, Fácil Instalación, Ideal para 6-15㎡ Dormitorios/Comedores/Pasillos, Vida Útil 50000h</t>
-  </si>
-  <si>
-    <t>4199</t>
-  </si>
-  <si>
-    <t>3220</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>3.00%</t>
-  </si>
-  <si>
-    <t>604713374312366</t>
-  </si>
-  <si>
-    <t>Mascarillas Infantiles KF94 10 pcs, Cuatro Capas de Protección con Tejido de Fusión Filtrante, Patrones Divertidos, Piel Amigable y Transpirable</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>233</t>
+    <t>2.69%</t>
+  </si>
+  <si>
+    <t>605450766548595</t>
+  </si>
+  <si>
+    <t>TIANLAI Lámpara de ventilador integrada para el hogar, base de rosca E27, 2 en 1 Silenciosa, Iluminación 180°, Instalación Sin Taladrar, bombilla para ventilador de techo de dormitorio, luz de ventilador LED，Perfecta para Pequeños Espacios Interiores</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>1.76%</t>
-  </si>
-  <si>
-    <t>604758890925204</t>
-  </si>
-  <si>
-    <t>MEGALUZ Lámpara Techo Empotrada LED 18W , Luz Fría 6500K Ajustable, Cuerpo Ultradelgado, Tamaño de Abertura Ajustable, Hecha de Aleación de Aluminio de Alta Calidad, Anticorrosivo y Antirroto, Voltaje de Trabajo 85-265V/60Hz, Ideal para Sala, Dormitorio, Escalera y Pasillo</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>2.37%</t>
-  </si>
-  <si>
-    <t>604862842503270</t>
-  </si>
-  <si>
-    <t>Megaluz Ventilador de techo con luz led y control remoto, 13”, luz blanca fría, neutra y cálida, 6 aspas desmontables, Abanico de techo enchufe E27, 4 velocidades y motor silencioso (Blanco)</t>
-  </si>
-  <si>
-    <t>2228</t>
-  </si>
-  <si>
-    <t>1738</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>2.96%</t>
-  </si>
-  <si>
-    <t>604986910049088</t>
-  </si>
-  <si>
-    <t>TIANLAI Ventilador de Techo con Luz E27 10", 2 en 1 Lampara Ventilador Silenciosa, Instalación Sin Taladrar, Ideal para Dormitorio y Espacios Pequeños，Silent 2-In-1 Ceiling Fan Lamp, Modern Design, Freshness, And Brightness for All Year Round, Ideal Solution for Small And Hot Spaces, Enjoy a Cool Summer, Ideal for Interiors, Living Room, Garage, Closet, Laundry Room, Bedroom, And Bathroom.</t>
-  </si>
-  <si>
-    <t>605025514435220</t>
-  </si>
-  <si>
-    <t>Linkbits Auriculares inalámbricos de orejas de gato con Inalámbrico 5.3, luces RGB, conductores de 40 mm para sonido Hi-Fi, batería de larga duración de 10 horas, botones multifuncionales, ideales para juegos y música, compatibles con tarjeta TF y entrada AUX, y con diseño plegable y portátil</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>605056434809577</t>
-  </si>
-  <si>
-    <t>linkbit Audífonos Inalámbricos de Diadema Bluetooth 6.0 - Baja Latencia para Música y Juegos, Audio Hi-Res con Driver de 40mm, Plegable para Hogar, Oficina y Viajes</t>
-  </si>
-  <si>
-    <t>605174814855085</t>
-  </si>
-  <si>
-    <t>Cámara de Seguridad WiFi HD: Cámara de vigilancia con visión panorámica de 355°, visión nocturna a color HD y control remoto, para interior y exterior. Cuenta con sistema de seguridad para el hogar, control mediante aplicación móvil, alertas de alarma en tiempo real y monitoreo remoto. Ideal para viviendas, oficinas y granjas.</t>
-  </si>
-  <si>
-    <t>555</t>
-  </si>
-  <si>
-    <t>453</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2.52%</t>
-  </si>
-  <si>
-    <t>605180133239039</t>
-  </si>
-  <si>
-    <t>Linkbits Brazo de Monitor de Movimiento Completo, Soporta 1 o 2 Monitores/TV, Soporte de Resorte de Gas Ajustable con Inclinación/Giro/Rotación, Carga Máxima 12kg/26.4 lbs, Apto para Pantallas Planas/Curvas de 17-32", 2 Opciones de Montaje, Gestión de Cables, Robusto y Estable</t>
-  </si>
-  <si>
-    <t>37.50%</t>
-  </si>
-  <si>
-    <t>605180133257498</t>
-  </si>
-  <si>
-    <t>Linkbits Auriculares Inalámbricos De Tapa Completa Con Wireless 5.0, Transductores De 40mm Para Audio De Alta Resolución, Reducción De Ruido En Llamadas ENC, Almohadillas De Piel De Proteína Ultra Suaves, Ajuste Multidimensional Y Dobles Modos (Música/Juego)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>605252929601306</t>
-  </si>
-  <si>
-    <t>Cozyna Calefactor Eléctrico con Ventilador 2 en 1, 750W/1500W, Protección Sobrecalentamiento, Compacto y Energéticamente Eficiente para Hogar y Oficina</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>605406743132022</t>
-  </si>
-  <si>
-    <t>TIANLAI Luz Solar de Calle con Carga Automática, Resistente al Agua IP65, Detección de Movimiento Inteligente, Iluminación para Casa, Comunidad y Camino Rural, Sin Costos de Electricidad</t>
-  </si>
-  <si>
-    <t>681</t>
-  </si>
-  <si>
-    <t>572</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>2.35%</t>
-  </si>
-  <si>
-    <t>605447276868345</t>
-  </si>
-  <si>
-    <t>Linkbits Altavoz Portátil- Luces Ambientales Coloridas 360°, Conexión TWS, Driver de Rango Completo 57mm, Graves Potentes, Batería 1500mAh con 10 Horas de Reproducción y Reproducción Sin Conexión</t>
-  </si>
-  <si>
-    <t>1178</t>
-  </si>
-  <si>
-    <t>973</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>3.06%</t>
-  </si>
-  <si>
-    <t>605450766548595</t>
-  </si>
-  <si>
-    <t>TIANLAI Lámpara de ventilador integrada para el hogar, base de rosca E27, 2 en 1 Silenciosa, Iluminación 180°, Instalación Sin Taladrar, bombilla para ventilador de techo de dormitorio, luz de ventilador LED，Perfecta para Pequeños Espacios Interiores</t>
-  </si>
-  <si>
-    <t>25.00%</t>
+    <t>20.00%</t>
   </si>
 </sst>
 </file>
@@ -904,10 +907,10 @@
         <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -915,25 +918,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -941,25 +944,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -967,25 +970,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -993,25 +996,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -1019,25 +1022,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -1045,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" t="s">
         <v>102</v>
@@ -1086,10 +1089,10 @@
         <v>108</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -1097,25 +1100,25 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
@@ -1123,25 +1126,25 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -1149,25 +1152,25 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" t="s">
         <v>127</v>
-      </c>
-      <c r="G20" t="s">
-        <v>127</v>
-      </c>
-      <c r="H20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="21">
@@ -1175,13 +1178,13 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
         <v>129</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>130</v>
-      </c>
-      <c r="D21" t="s">
-        <v>79</v>
       </c>
       <c r="E21" t="s">
         <v>131</v>
@@ -1233,19 +1236,19 @@
         <v>142</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H23" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -1259,19 +1262,19 @@
         <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="F24" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H24" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
@@ -1279,25 +1282,25 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" t="s">
         <v>146</v>
       </c>
-      <c r="C25" t="s">
-        <v>147</v>
-      </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="F25" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G25" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H25" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26">
@@ -1305,25 +1308,25 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" t="s">
         <v>148</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>149</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>150</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" t="s">
         <v>151</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>152</v>
-      </c>
-      <c r="G26" t="s">
-        <v>153</v>
-      </c>
-      <c r="H26" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="27">
@@ -1331,25 +1334,25 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" t="s">
         <v>155</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>156</v>
       </c>
-      <c r="D27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" t="s">
-        <v>127</v>
-      </c>
       <c r="F27" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="G27" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="H27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
@@ -1357,25 +1360,25 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G28" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H28" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29">
@@ -1383,25 +1386,25 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G29" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="H29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30">
@@ -1409,22 +1412,22 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G30" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="H30" t="s">
         <v>170</v>
@@ -1447,7 +1450,7 @@
         <v>174</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G31" t="s">
         <v>175</v>
@@ -1467,19 +1470,19 @@
         <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
